--- a/test cases nuevo.xlsx
+++ b/test cases nuevo.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29902"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29904"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\API PROJECTS\Postman_project_bookerAPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505D0AE3-BAFF-4FA7-8769-85DCFEDEE37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D9CD56-EECE-48BD-BACE-396CCF4DB442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" activeTab="8" xr2:uid="{4937A0C0-940E-4D7E-9F4D-E301FD197CC3}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="11844" firstSheet="8" activeTab="8" xr2:uid="{4937A0C0-940E-4D7E-9F4D-E301FD197CC3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
-    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
-    <sheet name="Hoja4" sheetId="4" r:id="rId4"/>
-    <sheet name="Hoja5" sheetId="5" r:id="rId5"/>
-    <sheet name="Hoja6" sheetId="6" r:id="rId6"/>
-    <sheet name="Hoja7" sheetId="7" r:id="rId7"/>
-    <sheet name="Hoja8" sheetId="8" r:id="rId8"/>
-    <sheet name="Hoja9" sheetId="9" r:id="rId9"/>
+    <sheet name="main" sheetId="1" r:id="rId1"/>
+    <sheet name="common verificacion" sheetId="2" r:id="rId2"/>
+    <sheet name="tips" sheetId="3" r:id="rId3"/>
+    <sheet name="general CRUD" sheetId="4" r:id="rId4"/>
+    <sheet name="create booking" sheetId="5" r:id="rId5"/>
+    <sheet name="Soap Request" sheetId="6" r:id="rId6"/>
+    <sheet name="full and partial update" sheetId="7" r:id="rId7"/>
+    <sheet name="SOAP UI Testcase" sheetId="8" r:id="rId8"/>
+    <sheet name="Integration Scenarios" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1945,7 +1945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2133,26 +2133,13 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2164,328 +2151,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="88">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Lato"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Lato"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Lato"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Lato"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Lato"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Lato"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Lato"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Lato"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Lato"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Lato"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Lato"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Lato"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4548,8 +4230,393 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Lato"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Lato"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Lato"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Lato"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Lato"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Lato"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Lato"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Lato"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Lato"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Lato"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Lato"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Lato"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -4562,50 +4629,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3B409686-6A6E-46C1-BF18-1D0B681641BA}" name="Tabla2" displayName="Tabla2" ref="A5:E11" totalsRowShown="0" headerRowDxfId="87" dataDxfId="86" tableBorderDxfId="85">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3B409686-6A6E-46C1-BF18-1D0B681641BA}" name="Tabla2" displayName="Tabla2" ref="A5:E11" totalsRowShown="0" headerRowDxfId="74" dataDxfId="73" tableBorderDxfId="72">
   <autoFilter ref="A5:E11" xr:uid="{3B409686-6A6E-46C1-BF18-1D0B681641BA}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D47BA81F-E63B-47A5-8856-0B1D53D30A29}" name="Test Scenario TID" dataDxfId="84"/>
-    <tableColumn id="2" xr3:uid="{C04A95EA-DB0F-480E-89EB-E87B63771A94}" name=" Test Scenario Description" dataDxfId="83"/>
-    <tableColumn id="3" xr3:uid="{8F8D25FF-901E-46F5-9949-113734DB54DA}" name="Priority" dataDxfId="82"/>
-    <tableColumn id="4" xr3:uid="{B6635D31-7FB4-483D-B395-C8D912991E36}" name="No. of Test cases" dataDxfId="81"/>
-    <tableColumn id="5" xr3:uid="{6F45ED35-BA8D-4DAB-A640-B340B5B4830D}" name="Linked Document" dataDxfId="80"/>
+    <tableColumn id="1" xr3:uid="{D47BA81F-E63B-47A5-8856-0B1D53D30A29}" name="Test Scenario TID" dataDxfId="71"/>
+    <tableColumn id="2" xr3:uid="{C04A95EA-DB0F-480E-89EB-E87B63771A94}" name=" Test Scenario Description" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{8F8D25FF-901E-46F5-9949-113734DB54DA}" name="Priority" dataDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{B6635D31-7FB4-483D-B395-C8D912991E36}" name="No. of Test cases" dataDxfId="68"/>
+    <tableColumn id="5" xr3:uid="{6F45ED35-BA8D-4DAB-A640-B340B5B4830D}" name="Linked Document" dataDxfId="67"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{EB5D4A86-FC95-4329-B54B-E6B05FC5DB17}" name="Tabla5" displayName="Tabla5" ref="A3:H10" headerRowCount="0" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78" tableBorderDxfId="77" totalsRowBorderDxfId="76">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{EB5D4A86-FC95-4329-B54B-E6B05FC5DB17}" name="Tabla5" displayName="Tabla5" ref="A3:H10" headerRowCount="0" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65" tableBorderDxfId="64" totalsRowBorderDxfId="63">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{AB0116BB-87D3-4405-934D-069E61326209}" name="Columna1" headerRowDxfId="75" dataDxfId="74"/>
-    <tableColumn id="2" xr3:uid="{52EB1AFB-16A7-46AE-9D65-2E5726D5673C}" name="Columna2" headerRowDxfId="73" dataDxfId="72"/>
-    <tableColumn id="3" xr3:uid="{88D56377-AC9C-4D51-A272-B97A3663D51F}" name="Columna3" headerRowDxfId="71" dataDxfId="70"/>
-    <tableColumn id="4" xr3:uid="{4188A1D8-0F31-41C5-85F1-D700897C65E4}" name="Columna4" headerRowDxfId="69" dataDxfId="68"/>
-    <tableColumn id="5" xr3:uid="{13A4A227-E24D-4EFF-A327-E33E39405294}" name="Columna5" headerRowDxfId="67" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{31B349E3-221A-4EFC-9EA3-EA4463498C6F}" name="Columna6" headerRowDxfId="65" dataDxfId="64"/>
-    <tableColumn id="7" xr3:uid="{B03C3CEC-A524-4A0B-8AB3-A881CE8D38FF}" name="Columna7" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{3DF960EC-5148-421C-9D8C-F6D3E28994E6}" name="Columna8" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{AB0116BB-87D3-4405-934D-069E61326209}" name="Columna1" headerRowDxfId="62" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{52EB1AFB-16A7-46AE-9D65-2E5726D5673C}" name="Columna2" headerRowDxfId="60" dataDxfId="59"/>
+    <tableColumn id="3" xr3:uid="{88D56377-AC9C-4D51-A272-B97A3663D51F}" name="Columna3" headerRowDxfId="58" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{4188A1D8-0F31-41C5-85F1-D700897C65E4}" name="Columna4" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{13A4A227-E24D-4EFF-A327-E33E39405294}" name="Columna5" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{31B349E3-221A-4EFC-9EA3-EA4463498C6F}" name="Columna6" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="7" xr3:uid="{B03C3CEC-A524-4A0B-8AB3-A881CE8D38FF}" name="Columna7" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{3DF960EC-5148-421C-9D8C-F6D3E28994E6}" name="Columna8" headerRowDxfId="48" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{53A87651-25FE-4D75-83E9-19BA1EEBA6C1}" name="Tabla6" displayName="Tabla6" ref="A2:E37" headerRowCount="0" totalsRowShown="0" headerRowDxfId="59" headerRowBorderDxfId="58" tableBorderDxfId="57" totalsRowBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{53A87651-25FE-4D75-83E9-19BA1EEBA6C1}" name="Tabla6" displayName="Tabla6" ref="A2:E37" headerRowCount="0" totalsRowShown="0" headerRowDxfId="46" headerRowBorderDxfId="45" tableBorderDxfId="44" totalsRowBorderDxfId="43">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{172466A6-8CF5-4AA1-A87D-A61312AB3F03}" name="Columna1" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{DEE02835-6AA0-4C26-A5C7-B8831212264E}" name="Columna2" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{CB09346F-9497-488E-8FF1-222742581C63}" name="Columna3" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{C46FA5AE-99A4-4A17-8228-0E9EB778808A}" name="Columna4" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{E2B1035D-3E97-4823-9515-AD21D5880F87}" name="Columna5" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{172466A6-8CF5-4AA1-A87D-A61312AB3F03}" name="Columna1" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{DEE02835-6AA0-4C26-A5C7-B8831212264E}" name="Columna2" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{CB09346F-9497-488E-8FF1-222742581C63}" name="Columna3" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{C46FA5AE-99A4-4A17-8228-0E9EB778808A}" name="Columna4" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{E2B1035D-3E97-4823-9515-AD21D5880F87}" name="Columna5" headerRowDxfId="34" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7DA01741-95AA-4633-83C8-FF209626C785}" name="Tabla9" displayName="Tabla9" ref="A1:N15" totalsRowShown="0" headerRowDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7DA01741-95AA-4633-83C8-FF209626C785}" name="Tabla9" displayName="Tabla9" ref="A1:N15" totalsRowShown="0" headerRowDxfId="32">
   <autoFilter ref="A1:N15" xr:uid="{7DA01741-95AA-4633-83C8-FF209626C785}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{E50F03CB-3BA3-4B08-939B-845A867AC6F8}" name="Scenario TID"/>
@@ -4628,42 +4695,42 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{319CF816-5D6A-48A0-BF62-0297D226DDEB}" name="Tabla7" displayName="Tabla7" ref="A1:N6" headerRowCount="0" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42" totalsRowBorderDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{319CF816-5D6A-48A0-BF62-0297D226DDEB}" name="Tabla7" displayName="Tabla7" ref="A1:N6" headerRowCount="0" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30" tableBorderDxfId="29" totalsRowBorderDxfId="28">
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{4580DC95-8BBB-42AD-8D8E-FD41BC9B42F7}" name="Columna1" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{FBF5A090-E73D-4099-9133-8970C1407F89}" name="Columna2" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{DF1D441C-6B26-40F3-9C12-D95C75FC0DCE}" name="Columna3" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{518050EC-3272-4FF5-BB01-EBF33C46DB85}" name="Columna4" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{44102063-B98F-405C-84BC-C89344CF5379}" name="Columna5" headerRowDxfId="32" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{2729F17B-337C-4A92-9ECB-E8B2CBB111A2}" name="Columna6" headerRowDxfId="30" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{71CBC962-E005-404E-ADD9-DA18774666CC}" name="Columna7" headerRowDxfId="28" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{3B3D3845-17E9-4DB1-9149-8AFC2AF90678}" name="Columna8" headerRowDxfId="26" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{A4E12058-E02F-40BE-BF42-422F15EA7626}" name="Columna9" headerRowDxfId="24" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{B821DA79-0729-42B5-AF0D-E350414F3656}" name="Columna10" headerRowDxfId="22" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{4B1451D0-ABA0-4AD3-A312-7BD8B6F42A87}" name="Columna11" headerRowDxfId="20" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{C10DCE7A-6D10-455C-A4DC-88709AC1006E}" name="Columna12" headerRowDxfId="18" dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{F6DBF316-72A2-46B6-A295-83CB431D7330}" name="Columna13" headerRowDxfId="16" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{CF64C5AC-C881-474E-8545-D90BF081B32B}" name="Columna14" headerRowDxfId="14" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{4580DC95-8BBB-42AD-8D8E-FD41BC9B42F7}" name="Columna1" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{FBF5A090-E73D-4099-9133-8970C1407F89}" name="Columna2" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{DF1D441C-6B26-40F3-9C12-D95C75FC0DCE}" name="Columna3" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{518050EC-3272-4FF5-BB01-EBF33C46DB85}" name="Columna4" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{44102063-B98F-405C-84BC-C89344CF5379}" name="Columna5" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{2729F17B-337C-4A92-9ECB-E8B2CBB111A2}" name="Columna6" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{71CBC962-E005-404E-ADD9-DA18774666CC}" name="Columna7" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{3B3D3845-17E9-4DB1-9149-8AFC2AF90678}" name="Columna8" headerRowDxfId="13" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{A4E12058-E02F-40BE-BF42-422F15EA7626}" name="Columna9" headerRowDxfId="11" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{B821DA79-0729-42B5-AF0D-E350414F3656}" name="Columna10" headerRowDxfId="9" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{4B1451D0-ABA0-4AD3-A312-7BD8B6F42A87}" name="Columna11" headerRowDxfId="7" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{C10DCE7A-6D10-455C-A4DC-88709AC1006E}" name="Columna12" headerRowDxfId="5" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{F6DBF316-72A2-46B6-A295-83CB431D7330}" name="Columna13" headerRowDxfId="3" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{CF64C5AC-C881-474E-8545-D90BF081B32B}" name="Columna14" headerRowDxfId="1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8162A8C7-8567-45D4-9EAC-33539BAA2E3F}" name="Tabla8" displayName="Tabla8" ref="A1:K7" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8162A8C7-8567-45D4-9EAC-33539BAA2E3F}" name="Tabla8" displayName="Tabla8" ref="A1:K7" totalsRowShown="0" headerRowDxfId="87" dataDxfId="86">
   <autoFilter ref="A1:K7" xr:uid="{8162A8C7-8567-45D4-9EAC-33539BAA2E3F}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{82183394-79D2-4A26-A777-B8EB99811BB0}" name="Scenario TID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{0B7F976B-63D0-45AF-9538-BA0E65C76406}" name=" Test Scenario" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{12E7240A-E159-405E-997B-D88AFF3FEE82}" name="Test Case Id" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{24E7E901-7E43-48AA-AE79-6EE555DDE78D}" name="Test Case Title" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{3C28B388-258A-46EE-9C97-CD50DD6839E1}" name="Pre Condition" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{274BE966-38F7-4B10-9766-80C947C99151}" name="Steps to Execute" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{ED27832A-5C7A-457E-B0E7-AF5448D5D4F0}" name="Expected Result" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{F7C34EEB-3E1C-46E5-9CAA-862391CC4A2F}" name="Actual Result" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{6021B049-5430-4C74-A5FD-63AAC0A4EF51}" name="Status" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{397EA284-AEE8-4ECE-A7E8-7E6BACBCE1AC}" name="Executed QA Name " dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{663533A9-E328-4837-8057-C66A75B9F010}" name="Misc (Comments)" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{82183394-79D2-4A26-A777-B8EB99811BB0}" name="Scenario TID" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{0B7F976B-63D0-45AF-9538-BA0E65C76406}" name=" Test Scenario" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{12E7240A-E159-405E-997B-D88AFF3FEE82}" name="Test Case Id" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{24E7E901-7E43-48AA-AE79-6EE555DDE78D}" name="Test Case Title" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{3C28B388-258A-46EE-9C97-CD50DD6839E1}" name="Pre Condition" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{274BE966-38F7-4B10-9766-80C947C99151}" name="Steps to Execute" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{ED27832A-5C7A-457E-B0E7-AF5448D5D4F0}" name="Expected Result" dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{F7C34EEB-3E1C-46E5-9CAA-862391CC4A2F}" name="Actual Result" dataDxfId="78"/>
+    <tableColumn id="9" xr3:uid="{6021B049-5430-4C74-A5FD-63AAC0A4EF51}" name="Status" dataDxfId="77"/>
+    <tableColumn id="10" xr3:uid="{397EA284-AEE8-4ECE-A7E8-7E6BACBCE1AC}" name="Executed QA Name " dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{663533A9-E328-4837-8057-C66A75B9F010}" name="Misc (Comments)" dataDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4674,10 +4741,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText" lastClr="5C6A72"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FDF6E3"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -5006,34 +5073,30 @@
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:6" ht="16.8">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="84" t="s">
+      <c r="B2" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="84" t="s">
+      <c r="F2" s="82" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16.8">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="83" t="s">
+      <c r="E3" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="86">
+      <c r="F3" s="83">
         <v>46082</v>
       </c>
     </row>
@@ -5190,38 +5253,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.2">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
       <c r="H1" s="10"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="89" t="s">
+      <c r="A3" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="90" t="s">
+      <c r="C3" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="90" t="s">
+      <c r="D3" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="90" t="s">
+      <c r="E3" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90" t="s">
+      <c r="F3" s="85"/>
+      <c r="G3" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="91" t="s">
+      <c r="H3" s="86" t="s">
         <v>23</v>
       </c>
     </row>
